--- a/Tools&Utilities/dashboards/OSS_SLU_CICD_Dashboard.xlsx
+++ b/Tools&Utilities/dashboards/OSS_SLU_CICD_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danyu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EC3F9A0-A7C7-46AF-A78C-4C775FF5964D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC358F9F-2DE8-47BD-9A65-855F4550A089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1698,7 +1698,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>46064</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -1712,7 +1712,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
